--- a/out/LSTM-Mamba1_repeat_2_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.166666627777778</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.166666627777778</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.349999978125</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7499999781250004</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_2_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.6533333205555558</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.01333333222222222</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.01333333222222222</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.6533333205555558</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.4533333205555558</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.349999978125</v>
+        <v>0.2133333322222223</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.01333333222222222</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.6533333205555558</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-2.166666627777778</v>
+        <v>-1.319999973333334</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-2.166666627777778</v>
+        <v>-0.6533333205555558</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.01333333222222229</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.349999978125</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.8799999850000004</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7499999781250004</v>
+        <v>0.6799999850000004</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_2_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01043521892279387</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.005534009076654911</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002778695896267891</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.00123170018196106</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0002811159938573837</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6533333205555558</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0002550706267356873</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.01333333222222222</v>
+        <v>-0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.000530727207660675</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0008045881986618042</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001092510297894478</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001008752733469009</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0008512791246175766</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0007487200200557709</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0008123535662889481</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0008448250591754913</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0008758995682001114</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0009199026972055435</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0009854454547166824</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001039858907461166</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001073339954018593</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001131212338805199</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001176793128252029</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001197041943669319</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001226482912898064</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.00154220312833786</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001506738364696503</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.00138222798705101</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001286247745156288</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.00120871514081955</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001119911670684814</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001081021502614021</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001115415245294571</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.001152198761701584</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.00120186060667038</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001261552795767784</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00136711448431015</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001530306413769722</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001489175483584404</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001324241980910301</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.001328133046627045</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001332119107246399</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001367948949337006</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.001311611384153366</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0008581820875406265</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0006787590682506561</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.01333333222222222</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0002907942980527878</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6533333205555558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0009834021329879761</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001385355368256569</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001404903829097748</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001381473615765572</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0009872447699308395</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0009552966803312302</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0009911712259054184</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.001125602051615715</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.001188522204756737</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.001065924763679504</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.001009935513138771</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0008930880576372147</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0006666351109743118</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0005816351622343063</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0005543306469917297</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.000439302995800972</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0004924535751342773</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.000597367063164711</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.0005284659564495087</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0004031788557767868</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0002926494926214218</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0005040206015110016</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0008115731179714203</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0009910892695188522</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.001015054062008858</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.00093081034719944</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0008472297340631485</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.319999973333334</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0006812103092670441</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.319999973333334</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0005551017820835114</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.319999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.0004891995340585709</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.319999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.000403430312871933</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.319999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0002849791198968887</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.319999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0001818221062421799</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.319999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.0001007430255413055</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.319999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-1.036934554576874e-05</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4533333205555558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>5.884841084480286e-05</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2133333322222223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0001393966376781464</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.0001316182315349579</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0001092087477445602</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>6.250850856304169e-05</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>1.531653106212616e-05</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8799999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>6.532296538352966e-05</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8799999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.000103924423456192</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8799999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.0002068020403385162</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8799999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.000108690932393074</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8799999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>9.838491678237915e-06</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.01333333222222222</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-2.210959792137146e-06</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6533333205555558</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-4.900991916656494e-05</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-6.369128823280334e-05</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.319999973333334</v>
+        <v>-0.16</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-2.969801425933838e-05</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6533333205555558</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.0001330003142356873</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.01333333222222229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0002082418650388718</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.0002687945961952209</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.0003210268914699554</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0004225149750709534</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.0004429109394550323</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.0005052071064710617</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.000581568107008934</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0006154756993055344</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.0006676483899354935</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.8799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.0007173959165811539</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0007546842098236084</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.000797683373093605</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.0008543264120817184</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.0008869282901287079</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0009644497185945511</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.001010404899716377</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.001065196469426155</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.001062585040926933</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.001075265929102898</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.001288812607526779</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.001349795609712601</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.00156128965318203</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.001280143857002258</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.6799999850000004</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.001120470464229584</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0007971785962581635</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0005555115640163422</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0005157608538866043</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6799999850000004</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0004954114556312561</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6799999850000004</v>
+        <v>-1</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.0006764475256204605</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.6799999850000004</v>
+        <v>-1.14</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_2_000002.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.01043521892279387</v>
+        <v>-0.01043521147221327</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.005534009076654911</v>
+        <v>-0.005534001626074314</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.002778695896267891</v>
+        <v>-0.002778679132461548</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.00123170018196106</v>
+        <v>-0.001231679692864418</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0002811159938573837</v>
+        <v>-0.0002810955047607422</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.0002550706267356873</v>
+        <v>0.000255092978477478</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.16</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.0008045881986618042</v>
+        <v>0.0008045993745326996</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.001092510297894478</v>
+        <v>0.001092523336410522</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.001008752733469009</v>
+        <v>0.001008769497275352</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.0008512791246175766</v>
+        <v>0.0008513089269399643</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0007487200200557709</v>
+        <v>0.0007487442344427109</v>
       </c>
       <c r="JB13" t="n">
         <v>0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.0008123535662889481</v>
+        <v>0.0008123815059661865</v>
       </c>
       <c r="JB14" t="n">
         <v>0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0008448250591754913</v>
+        <v>0.0008448492735624313</v>
       </c>
       <c r="JB15" t="n">
         <v>0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0008758995682001114</v>
+        <v>0.0008759181946516037</v>
       </c>
       <c r="JB16" t="n">
         <v>0.1199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0009199026972055435</v>
+        <v>0.0009198784828186035</v>
       </c>
       <c r="JB17" t="n">
         <v>0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0009854454547166824</v>
+        <v>0.0009854733943939209</v>
       </c>
       <c r="JB18" t="n">
         <v>0.2599999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.001039858907461166</v>
+        <v>0.001039875671267509</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.001073339954018593</v>
+        <v>0.001073369756340981</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.001131212338805199</v>
+        <v>0.001131245866417885</v>
       </c>
       <c r="JB21" t="n">
         <v>0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.001176793128252029</v>
+        <v>0.001176809892058372</v>
       </c>
       <c r="JB22" t="n">
         <v>0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.001197041943669319</v>
+        <v>0.001197068020701408</v>
       </c>
       <c r="JB23" t="n">
         <v>0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.001226482912898064</v>
+        <v>0.001226514577865601</v>
       </c>
       <c r="JB24" t="n">
         <v>0.9999999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.00154220312833786</v>
+        <v>0.001542253419756889</v>
       </c>
       <c r="JB25" t="n">
         <v>0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.001506738364696503</v>
+        <v>0.001506781205534935</v>
       </c>
       <c r="JB26" t="n">
         <v>0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.00138222798705101</v>
+        <v>0.001382270827889442</v>
       </c>
       <c r="JB27" t="n">
         <v>0.2599999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001286247745156288</v>
+        <v>0.001286286860704422</v>
       </c>
       <c r="JB28" t="n">
         <v>0.1199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.00120871514081955</v>
+        <v>0.001208741217851639</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.02000000000000007</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.001119911670684814</v>
+        <v>0.001119945198297501</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.001081021502614021</v>
+        <v>0.001081056892871857</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.001115415245294571</v>
+        <v>0.001115445047616959</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.001152198761701584</v>
+        <v>0.001152215525507927</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.16</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.00120186060667038</v>
+        <v>0.001201868057250977</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.001261552795767784</v>
+        <v>0.001261617988348007</v>
       </c>
       <c r="JB35" t="n">
         <v>0.1199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.00136711448431015</v>
+        <v>0.00136716291308403</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.001530306413769722</v>
+        <v>0.001530339941382408</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.001489175483584404</v>
+        <v>0.001489205285906792</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.001324241980910301</v>
+        <v>0.001324271783232689</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.001328133046627045</v>
+        <v>0.001328162848949432</v>
       </c>
       <c r="JB40" t="n">
         <v>0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.001332119107246399</v>
+        <v>0.001332147046923637</v>
       </c>
       <c r="JB41" t="n">
         <v>0.5799999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.001367948949337006</v>
+        <v>0.001368001103401184</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.3</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.001311611384153366</v>
+        <v>0.001311631873250008</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.5799999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.0008581820875406265</v>
+        <v>0.0008582137525081635</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.0006787590682506561</v>
+        <v>0.0006787627935409546</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.8599999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0002907942980527878</v>
+        <v>-0.000290771946310997</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0009834021329879761</v>
+        <v>-0.0009833760559558868</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001385355368256569</v>
+        <v>-0.001385344192385674</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001404903829097748</v>
+        <v>-0.001404896378517151</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001381473615765572</v>
+        <v>-0.001381432637572289</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.0009872447699308395</v>
+        <v>-0.0009872335940599442</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0009552966803312302</v>
+        <v>-0.0009553004056215286</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.0009911712259054184</v>
+        <v>-0.0009911768138408661</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.001125602051615715</v>
+        <v>-0.001125598326325417</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.001188522204756737</v>
+        <v>-0.00118851475417614</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.001065924763679504</v>
+        <v>-0.001065921038389206</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.001009935513138771</v>
+        <v>-0.001009929925203323</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.0008930880576372147</v>
+        <v>-0.0008930843323469162</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.0006666351109743118</v>
+        <v>-0.0006666276603937149</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0005816351622343063</v>
+        <v>-0.0005816239863634109</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0005543306469917297</v>
+        <v>-0.0005543343722820282</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.000439302995800972</v>
+        <v>-0.0004392974078655243</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.0004924535751342773</v>
+        <v>-0.0004924405366182327</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.000597367063164711</v>
+        <v>-0.0005973502993583679</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.0005284659564495087</v>
+        <v>-0.0005284566432237625</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.2599999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0004031788557767868</v>
+        <v>-0.0004031658172607422</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.2599999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.0002926494926214218</v>
+        <v>-0.0002926662564277649</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.2599999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.0005040206015110016</v>
+        <v>-0.0005040168762207031</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.2599999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0008115731179714203</v>
+        <v>-0.0008115600794553757</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.2599999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0009910892695188522</v>
+        <v>-0.0009910687804222107</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.3999999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.001015054062008858</v>
+        <v>-0.001015029847621918</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.00093081034719944</v>
+        <v>-0.0009307861328125</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.0008472297340631485</v>
+        <v>-0.0008472111076116562</v>
       </c>
       <c r="JB73" t="n">
         <v>0.16</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.0006812103092670441</v>
+        <v>-0.0006811898201704025</v>
       </c>
       <c r="JB74" t="n">
         <v>0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.0005551017820835114</v>
+        <v>-0.0005551129579544067</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.0004891995340585709</v>
+        <v>-0.0004891958087682724</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.000403430312871933</v>
+        <v>-0.0004034265875816345</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.0002849791198968887</v>
+        <v>-0.0002849772572517395</v>
       </c>
       <c r="JB78" t="n">
         <v>0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.0001818221062421799</v>
+        <v>-0.0001818239688873291</v>
       </c>
       <c r="JB79" t="n">
         <v>0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.0001007430255413055</v>
+        <v>-0.0001007318496704102</v>
       </c>
       <c r="JB80" t="n">
         <v>0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-1.036934554576874e-05</v>
+        <v>-1.034513115882874e-05</v>
       </c>
       <c r="JB81" t="n">
         <v>0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>5.884841084480286e-05</v>
+        <v>5.887448787689209e-05</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.0001393966376781464</v>
+        <v>0.0001394171267747879</v>
       </c>
       <c r="JB83" t="n">
         <v>0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.0001316182315349579</v>
+        <v>0.0001316331326961517</v>
       </c>
       <c r="JB84" t="n">
         <v>0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0001092087477445602</v>
+        <v>0.0001092106103897095</v>
       </c>
       <c r="JB85" t="n">
         <v>0.2599999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>6.250850856304169e-05</v>
+        <v>6.251595914363861e-05</v>
       </c>
       <c r="JB86" t="n">
         <v>0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1.531653106212616e-05</v>
+        <v>1.532025635242462e-05</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.02000000000000007</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>6.532296538352966e-05</v>
+        <v>6.532855331897736e-05</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.02000000000000007</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.000103924423456192</v>
+        <v>0.0001039206981658936</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.02000000000000007</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.0002068020403385162</v>
+        <v>0.0002068206667900085</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.000108690932393074</v>
+        <v>0.0001087076961994171</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.02000000000000007</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>9.838491678237915e-06</v>
+        <v>9.858980774879456e-06</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.02000000000000007</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-2.210959792137146e-06</v>
+        <v>-2.190470695495605e-06</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-4.900991916656494e-05</v>
+        <v>-4.899315536022186e-05</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.3</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-6.369128823280334e-05</v>
+        <v>-6.367452442646027e-05</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.16</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-2.969801425933838e-05</v>
+        <v>-2.968311309814453e-05</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.02000000000000007</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.0001330003142356873</v>
+        <v>0.0001330152153968811</v>
       </c>
       <c r="JB97" t="n">
         <v>0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.0003210268914699554</v>
+        <v>0.0003210343420505524</v>
       </c>
       <c r="JB100" t="n">
         <v>0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.0004225149750709534</v>
+        <v>0.0004225336015224457</v>
       </c>
       <c r="JB101" t="n">
         <v>0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.0004429109394550323</v>
+        <v>0.0004429202526807785</v>
       </c>
       <c r="JB102" t="n">
         <v>0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.0005052071064710617</v>
+        <v>0.0005052275955677032</v>
       </c>
       <c r="JB103" t="n">
         <v>0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.000581568107008934</v>
+        <v>0.0005815699696540833</v>
       </c>
       <c r="JB104" t="n">
         <v>0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.0006154756993055344</v>
+        <v>0.0006154812872409821</v>
       </c>
       <c r="JB105" t="n">
         <v>0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.0006676483899354935</v>
+        <v>0.0006676800549030304</v>
       </c>
       <c r="JB106" t="n">
         <v>0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.0007173959165811539</v>
+        <v>0.0007174182683229446</v>
       </c>
       <c r="JB107" t="n">
         <v>0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.0007546842098236084</v>
+        <v>0.0007547046989202499</v>
       </c>
       <c r="JB108" t="n">
         <v>0.3999999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.000797683373093605</v>
+        <v>0.0007976982742547989</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3999999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.0008543264120817184</v>
+        <v>0.0008543431758880615</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3999999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.0008869282901287079</v>
+        <v>0.0008869506418704987</v>
       </c>
       <c r="JB111" t="n">
         <v>0.3999999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.0009644497185945511</v>
+        <v>0.000964481383562088</v>
       </c>
       <c r="JB112" t="n">
         <v>0.3999999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.001010404899716377</v>
+        <v>0.001010425388813019</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3999999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.001065196469426155</v>
+        <v>0.001065203920006752</v>
       </c>
       <c r="JB114" t="n">
         <v>0.3999999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.001062585040926933</v>
+        <v>0.001062601804733276</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3999999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.001075265929102898</v>
+        <v>0.00107528455555439</v>
       </c>
       <c r="JB116" t="n">
         <v>0.3999999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.001288812607526779</v>
+        <v>0.00128881074488163</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3999999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.001349795609712601</v>
+        <v>0.001349793747067451</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3999999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.00156128965318203</v>
+        <v>0.00156131200492382</v>
       </c>
       <c r="JB119" t="n">
         <v>0.3999999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.001280143857002258</v>
+        <v>0.001280194148421288</v>
       </c>
       <c r="JB120" t="n">
         <v>0.2599999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.001120470464229584</v>
+        <v>0.00112047977745533</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.0007971785962581635</v>
+        <v>0.000797199085354805</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.0005555115640163422</v>
+        <v>0.0005555376410484314</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.0005157608538866043</v>
+        <v>0.0005157962441444397</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.8599999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.0004954114556312561</v>
+        <v>0.0004954133182764053</v>
       </c>
       <c r="JB125" t="n">
         <v>-1</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.0006764475256204605</v>
+        <v>0.0006764456629753113</v>
       </c>
       <c r="JB126" t="n">
         <v>-1.14</v>
